--- a/results/reliability_eval/unified_scores_table_09-03-1.xlsx
+++ b/results/reliability_eval/unified_scores_table_09-03-1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,12 +518,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P127</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -543,31 +543,31 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7469565217391304</v>
+        <v>0.9820945945945946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5787172809428369</v>
+        <v>0.6094235774415692</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.9867371630120714</v>
       </c>
       <c r="K2" t="n">
-        <v>0.578717680992443</v>
+        <v>0.6094235774415692</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.9867371630120714</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4234765110873748</v>
+        <v>0.3960349449279877</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7125515522191569</v>
+        <v>0.979229349872226</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9996491564954054</v>
+        <v>0.9999318496018069</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9998526421199809</v>
+        <v>0.9999975175456328</v>
       </c>
     </row>
     <row r="3">
@@ -578,12 +578,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P1412</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>neg1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -603,31 +603,31 @@
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8484004127966976</v>
+        <v>0.5954838709677419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5390826958703527</v>
+        <v>0.5576904357482563</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8594289369787165</v>
+        <v>0.6315329768688995</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5390833169035549</v>
+        <v>0.5576904357482563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.859429343759079</v>
+        <v>0.6315329768688995</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4637793149407588</v>
+        <v>0.4444059255956959</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8347486533499999</v>
+        <v>0.5720459719592944</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9990879506392875</v>
+        <v>0.9975862481422155</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9997996229467819</v>
+        <v>0.9980363831433818</v>
       </c>
     </row>
     <row r="4">
@@ -638,7 +638,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P127</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,31 +663,31 @@
         <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8534288638689866</v>
+        <v>0.7469565217391304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4947732900860435</v>
+        <v>0.5787172809428369</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8486241418652098</v>
+        <v>0.7839669903453134</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4947729550781172</v>
+        <v>0.578717680992443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.848624500736185</v>
+        <v>0.7839669903453134</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5061556031415703</v>
+        <v>0.4234765110873748</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8524127388315546</v>
+        <v>0.7125515522191569</v>
       </c>
       <c r="O4" t="n">
-        <v>0.997102348941576</v>
+        <v>0.9996491564954054</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9993914823434928</v>
+        <v>0.9998526421199809</v>
       </c>
     </row>
     <row r="5">
@@ -698,7 +698,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P1376</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -723,31 +723,31 @@
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.697008547008547</v>
+        <v>0.5980645161290322</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.509683558404514</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6769290861434174</v>
+        <v>0.6037327682441102</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.509683558404514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6769290861434173</v>
+        <v>0.6037327682441102</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5403673882005813</v>
+        <v>0.4973921342735205</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7188791760896567</v>
+        <v>0.60705048777457</v>
       </c>
       <c r="O5" t="n">
-        <v>0.998915148061319</v>
+        <v>0.9977226417355867</v>
       </c>
       <c r="P5" t="n">
-        <v>0.999417524526577</v>
+        <v>0.9981647398993689</v>
       </c>
     </row>
     <row r="6">
@@ -758,12 +758,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>toy-qa-dataset</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neg1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,31 +783,31 @@
         <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.9216216216216216</v>
       </c>
       <c r="I6" t="n">
-        <v>0.798970588235294</v>
+        <v>0.5972221344423096</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.9378063277674111</v>
       </c>
       <c r="K6" t="n">
-        <v>0.798970588235294</v>
+        <v>0.5972237144807362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.9378063558090117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1845588235294118</v>
+        <v>0.4014601135099605</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7056326939277201</v>
+        <v>0.8999185540887157</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.9997859047932045</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9999772485482282</v>
       </c>
     </row>
     <row r="7">
@@ -818,12 +818,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>toy-qa-dataset</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -843,31 +843,31 @@
         <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.968520461699895</v>
       </c>
       <c r="I7" t="n">
-        <v>0.798970588235294</v>
+        <v>0.6819371614301193</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.981414024424242</v>
       </c>
       <c r="K7" t="n">
-        <v>0.798970588235294</v>
+        <v>0.6819378837125317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.9814140270832503</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1845588235294118</v>
+        <v>0.3112258938244853</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7056326939277201</v>
+        <v>0.9508670515289894</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.9991404839292164</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.9999635881553406</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +878,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P1412</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,31 +903,31 @@
         <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8534288638689866</v>
+        <v>0.4789473684210526</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4947732900860435</v>
+        <v>0.4760156115404097</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8486241418652098</v>
+        <v>0.4657476840625634</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4947729550781172</v>
+        <v>0.4760165717489823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.848624500736185</v>
+        <v>0.4657477308617137</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5061556031415703</v>
+        <v>0.5246365621221446</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8524127388315546</v>
+        <v>0.4992602966374592</v>
       </c>
       <c r="O8" t="n">
-        <v>0.997102348941576</v>
+        <v>0.9944391334241393</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9993914823434928</v>
+        <v>0.9929965375806464</v>
       </c>
     </row>
     <row r="9">
@@ -938,7 +938,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P127</t>
+          <t>P159</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -963,31 +963,31 @@
         <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7469565217391304</v>
+        <v>0.9611168562564633</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5787172809428369</v>
+        <v>0.6290362920026189</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.9725986506352906</v>
       </c>
       <c r="K9" t="n">
-        <v>0.578717680992443</v>
+        <v>0.6290362920026189</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.9725986519489032</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4234765110873748</v>
+        <v>0.3711491399163954</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7125515522191569</v>
+        <v>0.9519419572812506</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9996491564954054</v>
+        <v>0.9997933922136908</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9998526421199809</v>
+        <v>0.9999891372819029</v>
       </c>
     </row>
     <row r="10">
@@ -998,12 +998,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P1412</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>neg1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1023,31 +1023,31 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2375</v>
+        <v>0.8484004127966976</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5390826958703527</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.8594289369787165</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5390833169035549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.859429343759079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4886362120775321</v>
+        <v>0.4637793149407588</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2389801701314956</v>
+        <v>0.8347486533499999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9952076786574728</v>
+        <v>0.9990879506392875</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9827497898003604</v>
+        <v>0.9997996229467819</v>
       </c>
     </row>
     <row r="11">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P108</t>
+          <t>P264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>neg1</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1083,31 +1083,31 @@
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5133159268929504</v>
+        <v>0.920979020979021</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.6977110458574768</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.9515472313731704</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.6977110458574768</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.9515472313731704</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4603038401756906</v>
+        <v>0.3033013560660869</v>
       </c>
       <c r="N11" t="n">
-        <v>0.508019239006987</v>
+        <v>0.8904375476666516</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9976499635433266</v>
+        <v>0.9992201668074024</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9973416212698993</v>
+        <v>0.9999114235623868</v>
       </c>
     </row>
     <row r="12">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P108</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1143,31 +1143,31 @@
         <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5133159268929504</v>
+        <v>0.8534288638689866</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.4947732900860435</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.8486241418652098</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.4947729550781172</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.848624500736185</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4603038401756906</v>
+        <v>0.5061556031415703</v>
       </c>
       <c r="N12" t="n">
-        <v>0.508019239006987</v>
+        <v>0.8524127388315546</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9976499635433266</v>
+        <v>0.997102348941576</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9973416212698993</v>
+        <v>0.9993914823434928</v>
       </c>
     </row>
     <row r="13">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P1376</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1203,31 +1203,31 @@
         <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8534288638689866</v>
+        <v>0.697008547008547</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4947732900860435</v>
+        <v>0.4657387413642067</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8486241418652098</v>
+        <v>0.6769290861434174</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4947729550781172</v>
+        <v>0.4657387413642067</v>
       </c>
       <c r="L13" t="n">
-        <v>0.848624500736185</v>
+        <v>0.6769290861434173</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5061556031415703</v>
+        <v>0.5403673882005813</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8524127388315546</v>
+        <v>0.7188791760896567</v>
       </c>
       <c r="O13" t="n">
-        <v>0.997102348941576</v>
+        <v>0.998915148061319</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9993914823434928</v>
+        <v>0.999417524526577</v>
       </c>
     </row>
     <row r="14">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>toy-qa-dataset</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1263,31 +1263,31 @@
         <v>0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.3933892969569779</v>
       </c>
       <c r="I14" t="n">
-        <v>0.798970588235294</v>
+        <v>0.4705341939999084</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.376331296424926</v>
       </c>
       <c r="K14" t="n">
-        <v>0.798970588235294</v>
+        <v>0.4705327867169468</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.3763305373068614</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1845588235294118</v>
+        <v>0.5285982737298245</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7056326939277201</v>
+        <v>0.410581293386488</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0.9991323523786704</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0.9984108145362187</v>
       </c>
     </row>
     <row r="15">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P1376</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>neg1</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1323,31 +1323,31 @@
         <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.697008547008547</v>
+        <v>0.9834368530020704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.7597348684210526</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6769290861434174</v>
+        <v>0.992363944062313</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.7597348684210526</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6769290861434173</v>
+        <v>0.992363944062313</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5403673882005813</v>
+        <v>0.2416032894736842</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7188791760896567</v>
+        <v>0.9761305171798338</v>
       </c>
       <c r="O15" t="n">
-        <v>0.998915148061319</v>
+        <v>0.9992697368421052</v>
       </c>
       <c r="P15" t="n">
-        <v>0.999417524526577</v>
+        <v>0.9999837262594506</v>
       </c>
     </row>
     <row r="16">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P108</t>
+          <t>toy-qa-dataset</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1383,31 +1383,31 @@
         <v>0.1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5133159268929504</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.9610000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.998109553191344</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5406411408100804</v>
+        <v>0.9610000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5441741798208495</v>
+        <v>0.998109553191344</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4603038401756906</v>
+        <v>0.029</v>
       </c>
       <c r="N16" t="n">
-        <v>0.508019239006987</v>
+        <v>0.9104617770479839</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9976499635433266</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9973416212698993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P1376</t>
+          <t>P264</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neg1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1443,31 +1443,31 @@
         <v>0.1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.697008547008547</v>
+        <v>0.3412587412587413</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.5155931552832983</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6769290861434174</v>
+        <v>0.3472821209712711</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.5155931552832983</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6769290861434173</v>
+        <v>0.3472821209712711</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5403673882005813</v>
+        <v>0.48405709667065</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7188791760896567</v>
+        <v>0.3260083143416232</v>
       </c>
       <c r="O17" t="n">
-        <v>0.998915148061319</v>
+        <v>0.9979667722436857</v>
       </c>
       <c r="P17" t="n">
-        <v>0.999417524526577</v>
+        <v>0.9952747536868766</v>
       </c>
     </row>
     <row r="18">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neg1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1503,31 +1503,31 @@
         <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2375</v>
+        <v>0.8393039918116684</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5760268370358863</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.8616865173027011</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5760268370358863</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.8616865173027011</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4886362120775321</v>
+        <v>0.4235189917663508</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2389801701314956</v>
+        <v>0.8179860805561486</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9952076786574728</v>
+        <v>0.9993063538915644</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9827497898003604</v>
+        <v>0.9998361607109759</v>
       </c>
     </row>
     <row r="19">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P127</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1563,31 +1563,31 @@
         <v>0.1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2375</v>
+        <v>0.8546086956521739</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5553910027594239</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.8714354909638249</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.5553910027594239</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.8714354909638249</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4886362120775321</v>
+        <v>0.4384969319179846</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2389801701314956</v>
+        <v>0.8378040931671161</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9952076786574728</v>
+        <v>0.9994347757505652</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9827497898003604</v>
+        <v>0.9998780386459163</v>
       </c>
     </row>
     <row r="20">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P1412</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neg1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1623,31 +1623,31 @@
         <v>0.1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8484004127966976</v>
+        <v>0.1449712643678161</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5390826958703527</v>
+        <v>0.5262831958183775</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8594289369787165</v>
+        <v>0.1541333693668091</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5390833169035549</v>
+        <v>0.5262831958183772</v>
       </c>
       <c r="L20" t="n">
-        <v>0.859429343759079</v>
+        <v>0.1541333693668091</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4637793149407588</v>
+        <v>0.472996518145629</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8347486533499999</v>
+        <v>0.1403024979185589</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9990879506392875</v>
+        <v>0.9950979747222068</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9997996229467819</v>
+        <v>0.9671630813436749</v>
       </c>
     </row>
     <row r="21">
@@ -1658,56 +1658,1436 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>P108</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4049608355091384</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5313595469412223</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4258960194623325</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5313595469412223</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4258960194623325</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4618184307764471</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3786074998888054</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.9975374349773348</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9956383200104504</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.7805376344086021</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5188697144547252</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.7864810464204722</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5188697144547252</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7864810795290103</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.49189946096751</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.7786182474714121</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.9966782015655236</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.9988660508396427</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P108</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5133159268929504</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5406411408100804</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5441741798208495</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5406411408100804</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5441741798208495</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4603038401756906</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.508019239006987</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9976499635433266</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9973416212698993</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P103</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9536335721596725</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.618116116638365</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9647402004115331</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.618116116638365</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9647402004115331</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3816170967120559</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.9418572674935798</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.9997368858131815</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.9999828756038533</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7901656314699793</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5005265287025522</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7912603756650283</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5005265287025522</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7912603844292602</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.499487561183553</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.796041703687667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9995462474981565</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9998484916734667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>toy-qa-dataset</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7761904761904762</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7065657224905364</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8581283480925073</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.7065657224905364</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8581283480925073</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2989165905234304</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7233311422728601</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9960187965017622</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9981234211476001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P176</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9831975560081466</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4369875868995496</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9815888635743031</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.4369875868995496</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9815888635743031</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5740388870580481</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.9884355276876652</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.9999795992027997</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9999994530067847</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P1376</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6311965811965812</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5450429176300023</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6548428386247492</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.5450786136754295</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6548428386247492</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4548080219605209</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6051252552961927</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9998113209027412</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9998531310417058</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P159</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7697001034126163</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4719454140948834</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7574997623835849</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.471946258711847</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.7574999255778028</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5284649490898076</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.781275126979887</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9998907729276855</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9999567737012314</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P108</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6963446475195822</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4723758197465214</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6802914711424632</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.4723758197465214</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6802914711424632</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5318079865984078</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.714111827317133</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9973142329693742</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9985738856547363</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P176</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9123217922606924</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4859498017747387</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.90980182985851</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.4859498017747386</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.909801920585209</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5116331995842721</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9145537543073914</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.9998736663175475</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9999847149148441</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P178</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.914527027027027</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5499190723508515</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9219475309162477</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.5499190723508515</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.9219480644789266</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.4466456091731144</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8946599978022879</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9996269370436184</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9999542124207927</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4923155941779181</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.369747484264414</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.4923184190366753</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3697476875640937</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5089512113377382</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.3770705998219999</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9996222349899454</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9992382256189261</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.510593220338983</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5454767293563975</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5373810108513996</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.5454766170896876</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5373809523438522</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.4478982998329471</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.4705913112389753</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.9994090280397334</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9993116654247108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P1376</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7658119658119659</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6332519022093325</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.821721103397907</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.6332519022093325</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.821721103397907</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3686136478428049</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.7315594959885379</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9993095835505734</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9997232907628104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P264</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>15</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3652680652680653</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5624616089137393</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.402393884153067</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.5624580935147685</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4023904644319581</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.439077784295588</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3301741923081988</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9979187666293019</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.9956501466792956</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>15</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.276867816091954</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4851010316859429</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.2676575171216576</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.4850973198065574</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2676557281303009</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5114112452004627</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.2767598650153381</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.9954869217600784</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.9866394053678984</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9623940677966102</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5906983341989195</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9710915414441912</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5906941483795453</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.9710912360453958</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.3939300968164518</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.9528223884313199</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.9997759811483098</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.9999885481593789</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6584470094438615</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.542119693269931</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6804986198422883</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.5421155072490377</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6804954093264417</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.4560042349802021</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.6307559981420964</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9990603484678796</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9994091519983905</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>15</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5122759596469454</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.2478499688916971</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.5122759596469454</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2478499688916971</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.4886362120775321</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.2389801701314956</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.9952076786574728</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9827497898003604</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P1412</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8942208462332302</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6501032187240511</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9265176107012241</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6501028809480247</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.9265175703355477</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.3492579342181188</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.8656566941240598</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.9966501062587083</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.9995144489396723</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P159</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>neg1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>15</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6559462254395036</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5266452973561638</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6733434528926472</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.526645321049297</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.67334349963493</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.4738662136918729</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.6476932679877369</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9998327027879851</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9998869685304232</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>P127</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>neg1</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>direct_answer</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.7469565217391304</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5787172809428369</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7839669903453134</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.578717680992443</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.7839669903453134</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.4234765110873748</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7125515522191569</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.9996491564954054</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.9998526421199809</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7243478260869565</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5599993183393231</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7567206141457</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.5599993183393231</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.7567206141457</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.4382359379082863</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.7087222934321332</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9995270032303143</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.9997743984531083</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P176</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>direct_answer</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>15</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.9304480651731161</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5491188226205583</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9385073947286824</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.5491188226205583</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9385073947286824</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.4492439874492254</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9219613525736453</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9999197990055718</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.999992121186533</v>
       </c>
     </row>
   </sheetData>
